--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/5-Project/Properties.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/5-Project/Properties.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,6 +228,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -595,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I31"/>
+  <dimension ref="B2:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -658,160 +661,179 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Method Double OneThird()</t>
-        </is>
-      </c>
+          <t>Spreadsheet Double OneThird()</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>return 1.0 / 3;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>= 1.0 / 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Test OneThird OneThirdTest</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>One Third</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="n">
+    <row r="19">
+      <c r="B19" s="8" t="n">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="B20" s="2" t="inlineStr">
+    <row r="21" ht="16.5" customHeight="1">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>"$properties" in a rule returns the properties of the table that runs, for example "$properties.description" or "$properties.tags".</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>SmartRules String DescribeSelf(String prefix)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>A rule reading its own properties</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>guide, properties</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="7" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>= prefix + ": " + $properties.description + ", tag " + $properties.tags[1]</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Test DescribeSelf DescribeSelfTest</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>prefix</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="7" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Prefix</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Info: A rule reading its own properties, tag properties</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B23:B24"/>
+  <mergeCells count="8">
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -824,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I36"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -899,154 +921,211 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Method Double GoldenRatio()</t>
-        </is>
-      </c>
+          <t>Spreadsheet Double GoldenRatio()</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>return (1 + sqrt(5)) / 2;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>= (1 + sqrt(5)) / 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Test GoldenRatio GoldenRatioTest</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D18" s="10" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Golden Ratio</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="8" t="n">
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="8" t="n">
         <v>1.618</v>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Method Double SquareRootOfTwo()</t>
-        </is>
-      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>return sqrt(2);</t>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Double SquareRootOfTwo()</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>= sqrt(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Test SquareRootOfTwo SquareRootOfTwoTest</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Square Root Of 2</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="8" t="n">
+    <row r="30">
+      <c r="B30" s="8" t="n">
         <v>1.4142</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Method String CategoryPrecision()</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>return PreciseCategory.precision + " in " + PreciseCategory.category;</t>
-        </is>
-      </c>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet String CategoryPrecision()</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>= PreciseCategory.precision + " in " + PreciseCategory.category</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Test CategoryPrecision CategoryPrecisionTest</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="7" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>4 in Precise</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
